--- a/BWI/bestwine_output/bestwine_Barbados.xlsx
+++ b/BWI/bestwine_output/bestwine_Barbados.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2242,107 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Armstrong Agencies Ltd.</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Armstrong Agencies Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>121891</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Barbados</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Bridgetown</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Saint Michael</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Lot 2 Lower Estate Heights</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>BB19187</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.armstrong.com.bb</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>admin@armstrong.com.bb</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>+1 246-426-2767</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1000003900500</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/armstrong-agencies-limited/</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ArmstrongAgencies/</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/armstrongagencies</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
